--- a/tests/fixtures/10_delivery_note/data-export-control.xlsx
+++ b/tests/fixtures/10_delivery_note/data-export-control.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -578,191 +578,192 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>line.item</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>line.ordered</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>line.delivered</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>line.unit</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>line.notes</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>USB-C Cables</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>box</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Wireless Mice</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E8" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F8" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>2 damaged in transit</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>HDMI Cables</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E9" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Laptop Stands</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Monitor Risers</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Backorder: 5 units</t>
         </is>
